--- a/data/trans_orig/IP16A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Estudios-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77232</t>
+          <t>77984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>83855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164205</t>
+          <t>163658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19443</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>52249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136710</t>
+          <t>137582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142509</t>
+          <t>142530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260628</t>
+          <t>260782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267145</t>
+          <t>267139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>22263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45189</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119906</t>
+          <t>120008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235983</t>
+          <t>235959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86636</t>
+          <t>86646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183815</t>
+          <t>183862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185901</t>
+          <t>185947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190873</t>
+          <t>190876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>372227</t>
+          <t>372764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377842</t>
+          <t>377841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98874</t>
+          <t>98732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104730</t>
+          <t>104767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>93514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193845</t>
+          <t>194103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201720</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>33148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72214</t>
+          <t>71831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154026</t>
+          <t>154486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160700</t>
+          <t>161039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143185</t>
+          <t>143430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300591</t>
+          <t>300104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308085</t>
+          <t>308086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3484</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3427</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19585</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16893</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19585</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16774</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,102 +1070,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2723</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3394</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3814</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4773</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86971</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84163</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>80038</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77984</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77313</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86971</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83855</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>252</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163658</t>
+          <t>163603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,102 +1413,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4078</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>767</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4552</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5567</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34453</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31188</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21784</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18798</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19314</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,65%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34453</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30714</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52249</t>
+          <t>52967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4706</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5206</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5611</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>141009</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>137263</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142520</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>123869</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>120599</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>120099</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>141009</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>137582</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>142530</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>399</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260782</t>
+          <t>260503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267139</t>
+          <t>267134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3477</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24896</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22263</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22063</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>86,44%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,107 +2668,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3386</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3079</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122787</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>120340</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>122787</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>120008</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>343</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235959</t>
+          <t>235924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1266</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3839</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3814</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43966</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41374</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>43966</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>41393</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,51%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>125</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86646</t>
+          <t>87277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5531</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3472,69 +3472,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>189605</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>185784</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>190870</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>186365</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>183862</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>183815</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>189605</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>185947</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>190876</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>536</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>372764</t>
+          <t>372223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>377846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4494</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3301</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1143</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7178</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4178</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96322</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>93198</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>102609</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98732</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104767</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99186</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>104673</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96322</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>93514</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194103</t>
+          <t>194535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201619</t>
+          <t>201715</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4622</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3660</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3598</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37043</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>33148</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34110</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,31%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>109</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71831</t>
+          <t>70611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4028</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1497</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8050</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8802</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>146755</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143330</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>158508</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>154486</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161039</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153734</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161075</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>146755</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>143430</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300104</t>
+          <t>300927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308086</t>
+          <t>308222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
